--- a/data/special-databases/categories.xlsx
+++ b/data/special-databases/categories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\special-databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7B3B21-B000-47C5-A230-D725C10BAC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B16662-62CE-4923-8037-29F03080C3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="258" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="35">
   <si>
     <t>lesbian</t>
   </si>
@@ -69,6 +69,78 @@
   </si>
   <si>
     <t>cis</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>behaviour</t>
+  </si>
+  <si>
+    <t>top-bottom</t>
+  </si>
+  <si>
+    <t>final string</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>breasts</t>
+  </si>
+  <si>
+    <t>tiny</t>
+  </si>
+  <si>
+    <t>small tits</t>
+  </si>
+  <si>
+    <t>isTeenAtShoot</t>
+  </si>
+  <si>
+    <t>teen</t>
+  </si>
+  <si>
+    <t>meaning</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>tiny,small tits</t>
+  </si>
+  <si>
+    <t>tiny,small tits,teen</t>
+  </si>
+  <si>
+    <t>tiny,teen</t>
+  </si>
+  <si>
+    <t>small tits,teen</t>
+  </si>
+  <si>
+    <t>size tiny , tits small , age teen</t>
+  </si>
+  <si>
+    <t>size tiny , tits normal , age not teen</t>
+  </si>
+  <si>
+    <t>size tiny , tits small , age not teen</t>
+  </si>
+  <si>
+    <t>size tiny , tits normal , age teen</t>
+  </si>
+  <si>
+    <t>size normal , tits small , age teen</t>
+  </si>
+  <si>
+    <t>size normal , tits small , age not teen</t>
+  </si>
+  <si>
+    <t>size normal , tits normal , age teen</t>
   </si>
 </sst>
 </file>
@@ -160,7 +232,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -183,109 +255,53 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,292 +590,455 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1605F2D5-8484-4D0C-86D0-D24E81A20C64}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="85.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="85.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="9.140625" style="4"/>
+    <col min="19" max="19" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="18" t="str">
-        <f>_xlfn.CONCAT(A1,"-",B1,"-",C1)</f>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>_xlfn.CONCAT(A2,"-",B2,"-",C2)</f>
         <v>bdsm-soft-maledom</v>
       </c>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="18" t="str">
-        <f t="shared" ref="E2:E6" si="0">_xlfn.CONCAT(A2,"-",B2,"-",C2)</f>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" ref="E3:E7" si="0">_xlfn.CONCAT(A3,"-",B3,"-",C3)</f>
         <v>bdsm-soft-femdom</v>
       </c>
-      <c r="J2" s="24"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="18" t="str">
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-soft-lesdom</v>
       </c>
-      <c r="J3" s="24"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="G4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="19" t="str">
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="10" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-hard-maledom</v>
       </c>
-      <c r="J4" s="24"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="19" t="str">
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-hard-femdom</v>
       </c>
-      <c r="J5" s="24"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B7" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="20" t="str">
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-hard-lesdom</v>
       </c>
-      <c r="J6" s="24"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J7" s="24"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="16" t="str">
-        <f>_xlfn.CONCAT(A8,"-",B8,"-",C8)</f>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="11" t="str">
+        <f>_xlfn.CONCAT(A9,"-",B9,"-",C9)</f>
         <v>normal-rough-cis</v>
       </c>
-      <c r="J8" s="24"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="21" t="str">
-        <f t="shared" ref="E9:E17" si="1">_xlfn.CONCAT(A9,"-",B9,"-",C9)</f>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="11" t="str">
+        <f t="shared" ref="E10:E18" si="1">_xlfn.CONCAT(A10,"-",B10,"-",C10)</f>
         <v>normal-rough-maledom</v>
       </c>
-      <c r="J9" s="24"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="21" t="str">
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="11" t="str">
         <f t="shared" si="1"/>
         <v>normal-rough-femdom</v>
       </c>
-      <c r="J10" s="24"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="21" t="str">
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="11" t="str">
         <f t="shared" si="1"/>
         <v>normal-rough-lesdom</v>
       </c>
-      <c r="J11" s="24"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="21" t="str">
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="11" t="str">
         <f t="shared" si="1"/>
         <v>normal-rough-lesbian</v>
       </c>
-      <c r="J12" s="24"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C14" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="22" t="str">
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="14" t="str">
         <f t="shared" si="1"/>
         <v>normal-sensual-cis</v>
       </c>
-      <c r="J13" s="24"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B15" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="22" t="str">
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="14" t="str">
         <f t="shared" si="1"/>
         <v>normal-sensual-maledom</v>
       </c>
-      <c r="J14" s="24"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="22" t="str">
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="14" t="str">
         <f t="shared" si="1"/>
         <v>normal-sensual-femdom</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="22" t="str">
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="14" t="str">
         <f t="shared" si="1"/>
         <v>normal-sensual-lesdom</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B18" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C18" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="17" t="str">
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="14" t="str">
         <f t="shared" si="1"/>
         <v>normal-sensual-lesbian</v>
       </c>
